--- a/data/trans_orig/IP31KM12_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM12_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,74 +720,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>37112</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>35758</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>99,14%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>95,52%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>46034</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>44112</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>99,01%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>94,88%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>42299</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>40728</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>42681</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>95,42%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>44895</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>43096</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>45285</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>95,17%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>162</t>
@@ -795,27 +795,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>90927</t>
+          <t>79412</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88934</t>
+          <t>77680</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>323</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>382</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>704</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>2436</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>153048</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>147719</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>155557</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>97,46%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>94,06%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>156335</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>152573</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>158260</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>98,14%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>95,78%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>99,35%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>177673</t>
+          <t>142868</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>172488</t>
+          <t>139297</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>180440</t>
+          <t>144465</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>334009</t>
+          <t>295916</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>327868</t>
+          <t>290330</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>337842</t>
+          <t>299237</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>3994</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>6221</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>7250</t>
+          <t>6644</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>3323</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13391</t>
+          <t>12230</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>199111</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>195098</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>97,49%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>171332</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>168000</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>172613</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>98,99%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>97,07%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>211432</t>
+          <t>172877</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>207176</t>
+          <t>169582</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174187</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,27 +1481,27 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>382765</t>
+          <t>371987</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>377941</t>
+          <t>367485</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>384839</t>
+          <t>374091</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5028</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1740</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>459</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5072</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>485</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,22 +1594,22 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2798</t>
+          <t>2811</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>707</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7313</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>291294</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>288773</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>292221</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>98,82%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>323</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>260984</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>253659</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>266816</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>95,16%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>92,49%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>97,28%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>339</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>304002</t>
+          <t>241501</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>301069</t>
+          <t>233767</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>246827</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>564986</t>
+          <t>532795</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>556558</t>
+          <t>524452</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>570737</t>
+          <t>538530</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>927</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3448</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>13283</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>7451</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>20608</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>7,51%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>13836</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>21570</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>14280</t>
+          <t>14763</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8529</t>
+          <t>9028</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22708</t>
+          <t>23106</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>931</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>680565</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>674888</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>684044</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>99,09%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>98,26%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>888</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>634685</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>626735</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>641562</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>97,18%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>95,96%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>98,23%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>931</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>738002</t>
+          <t>599545</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>731772</t>
+          <t>591684</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>741486</t>
+          <t>605462</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1372687</t>
+          <t>1280109</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1362794</t>
+          <t>1269948</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1380432</t>
+          <t>1287702</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6259</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2780</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>11936</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>18449</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>11572</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>26399</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6731</t>
+          <t>18663</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>12746</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>26524</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>25180</t>
+          <t>24922</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17435</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35073</t>
+          <t>35083</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
